--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0042.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0042.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Vitreum Dancer</t>
+          <t>Hologram Chiến Thuật: Vũ Công Vitreum</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Vitreum Dancer</t>
+          <t>Hologram Chiến Thuật: Vũ Công Vitreum</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Vitreum Dancer</t>
+          <t>Hologram Chiến Thuật: Vũ Công Vitreum</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Contamination</t>
+          <t>Nhiễm Khuẩn</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Nightmare: Inferno Rider</t>
+          <t>Ác Mộng: Inferno Rider</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Nightmare: Tempest Mephis</t>
+          <t>Ác Mộng: Tempest Mephis</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Nightmare: Impermanence Heron</t>
+          <t>Ác Mộng: Impermanence Heron</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Nightmare: Feilian Beringal</t>
+          <t>Ác Mộng: Feilian Beringal</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Nightmare: Crownless</t>
+          <t>Ác Mộng: Crownless</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Nightmare: Thundering Mephis</t>
+          <t>Ác Mộng: Thundering Mephis</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Nightmare: Mourning Aix</t>
+          <t>Ác Mộng: Mourning Aix</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Nightmare: Hecate</t>
+          <t>Ác Mộng: Hecate</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Đạt 2.000 Tactic Points ở Secluded Bog I</t>
+          <t>Nhận 2.000 Điểm Chiến Thuật ở Secluded Bog I.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Đạt 4.000 Tactic Points ở Secluded Bog II</t>
+          <t>Thu thập 4.000 Điểm Chiến Thuật trong Vùng Đầm Lầy Cô Độc II</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Đạt 8.000 Tactic Points ở Secluded Bog III</t>
+          <t>Thu thập 8.000 Điểm Chiến Thuật tại Vùng Đầm Lầy Cô Tịch III</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Đạt 2.000 Tactic Points ở Tide of Perils I</t>
+          <t>Nhận 2.000 Điểm Chiến Thuật ở Tide of Perils I.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Đạt 4.000 Tactic Points ở Tide of Perils II</t>
+          <t>Thu thập 4.000 Điểm Chiến Thuật trong Nguy Hiểm Dâng Trào II</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Đạt 8.000 Tactic Points ở Tide of Perils III</t>
+          <t>Thu thập 8.000 Điểm Chiến Thuật tại Nguy Hiểm Ngập Tràn III</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 3.000 Tactic Points</t>
+          <t>Thu thập tổng cộng 3.000 Điểm Chiến Thuật.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 12.000 Tactic Points</t>
+          <t>Tổng cộng đạt 12.000 Điểm Chiến Thuật.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 20.000 Tactic Points</t>
+          <t>Thu thập tổng cộng 20.000 Điểm Chiến Thuật</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 30.000 Tactic Points</t>
+          <t>Tổng cộng thu thập 30.000 Điểm Chiến Thuật.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 40.000 Tactic Points</t>
+          <t>Thu thập tổng cộng 40.000 Điểm Chiến Thuật.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 50.000 Tactic Points</t>
+          <t>Thu thập tổng cộng 50.000 Điểm Chiến Thuật</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 70.000 Tactic Points</t>
+          <t>Đạt tổng cộng 70.000 Điểm Chiến Thuật</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 90.000 Tactic Points</t>
+          <t>Thu thập tổng cộng 90.000 Điểm Chiến Thuật.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Mở khóa 1 Low-Capacity Variable</t>
+          <t>Mở khóa 1 Bộ Lưu Trữ Hạn Chế</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Mở khóa 2 Low-Capacity Variable</t>
+          <t>Mở khóa 2 Biến Số Dung Lượng Thấp</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Mở khóa 3 Low-Capacity Variable</t>
+          <t>Mở khóa 3 Biến Số Dung Lượng Thấp</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Mở khóa 4 Low-Capacity Variable</t>
+          <t>Mở khóa 4 Biến Số Dung Lượng Thấp</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Mở khóa 5 Low-Capacity Variable</t>
+          <t>Mở khóa 5 Biến Số Dung Lượng Thấp</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Roaming Variable</t>
+          <t>Biến Số Lang Thang</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Striking Variable</t>
+          <t>Biến Số Đòn Đánh</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Piercing Variable</t>
+          <t>Biến Thể Xuyên Thấu</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Wintry Variable</t>
+          <t>Biến Số Mùa Đông</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Frosty Variable</t>
+          <t>Biến Số Băng Giá</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Speeding Variable</t>
+          <t>Biến Số Tăng Tốc</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Rumbling Variable</t>
+          <t>Biến Số Gầm Ghè</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Thump Variable</t>
+          <t>Biến Thể Đập</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Dodging Variable</t>
+          <t>Biến số né tránh</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Rushing Variable</t>
+          <t>Biến Số Xông Phá</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Air Dash Variable</t>
+          <t>Biến Số Đột Kích Trên Không</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Summation Variable</t>
+          <t>Biến Số Tổng Hợp</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Intro Variable</t>
+          <t>Biến Số Khởi Động</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Aegis Variable</t>
+          <t>Biến Số Aegis</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Armor Variable</t>
+          <t>Biến Thể Áo Giáp</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Velocity Variable</t>
+          <t>Biến Số Vận Tốc</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Remedy Variable</t>
+          <t>Biến Số Trị Liệu</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Dashing Variable</t>
+          <t>Biến Số Phóng Tốc</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Bash Variable</t>
+          <t>Biến Số Bash</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Regen Variable</t>
+          <t>Biến số hồi phục</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Vengeance Variable</t>
+          <t>Biến Số Báo Thù</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>Không Khả Dụng</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Not Available</t>
+          <t>Không Khả Dụng</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Onslaught Varibale</t>
+          <t>Biến thể Tấn công dữ dội</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Pinnacle Variable</t>
+          <t>Biến Số Đỉnh Cao</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Fury Variable</t>
+          <t>Biến Số Phẫn Nộ</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Roaring Variable</t>
+          <t>Biến Số Gầm Thét</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Smite Variable</t>
+          <t>Biến Số Trừng Phạt</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Vitality Variable</t>
+          <t>Năng Lượng Biến Đổi</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Biến số không khả dụng trong thử thách này</t>
+          <t>Biến không khả dụng trong thử thách này</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Attribute Variable</t>
+          <t>Biến số Thuộc tính</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Water-Skiing Challenge</t>
+          <t>Thử thách Trượt Nước</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Data Researcher</t>
+          <t>Nhà Nghiên cứu Dữ liệu</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>KU-Repair</t>
+          <t>KU-Sửa chữa</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>KU-Repair dường như gặp chút trục trặc…</t>
+          <t>KU-Sửa chữa dường như gặp chút trục trặc…</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Supply Chest in Space Anchor</t>
+          <t>Rương Vật Tư tại Neo Không Gian</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Tactic Points đạt được trong giai đoạn này</t>
+          <t>Điểm Chiến Thuật Nhận Được Trong Giai Đoạn Này</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Time Bonus Points</t>
+          <t>Điểm Thưởng Thời Gian</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Tactic Points</t>
+          <t>Điểm Chiến Thuật</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Data Rewards</t>
+          <t>Phần thưởng Dữ liệu</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>Tôi...</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Rift Runner I</t>
+          <t>Kẻ Đột Kích Hư Không I</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Rift Runner II</t>
+          <t>Kẻ Đột Kích Hư Không II</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Rift Runner III</t>
+          <t>Kẻ Đột Kích Hư Không III</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Rift Runner IV</t>
+          <t>Kẻ Đột Kích Hư Không IV</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Rift Runner V</t>
+          <t>Kẻ Đột Kích Hư Không V</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Rift Runner VI</t>
+          <t>Kẻ Đột Kích Hư Không VI</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Rift Runner VII</t>
+          <t>Kẻ Đột Kích Hư Không VII</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Bắt Đầu</t>
+          <t>Bắt đầu</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Thousand Roars</t>
+          <t>Tiếng Gầm Ngàn Vực</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Unsheathe</t>
+          <t>Rút Kiếm</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Feather Fall</t>
+          <t>Rơi Nhẹ Nhàng</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Rumble</t>
+          <t>Ầm ầm</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Bladeline</t>
+          <t>Đường Kiếm</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Boundless</t>
+          <t>Vô Biên</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Động lực</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Refraction</t>
+          <t>Khúc xạ</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Reverberance</t>
+          <t>Dư Âm</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Breeze</t>
+          <t>Cơn Gió Nhẹ</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Current Flow</t>
+          <t>Dòng Chảy Hiện Tại</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Desolation</t>
+          <t>Hoang Tàn</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Harmony</t>
+          <t>Hòa Điệu</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Dodge Boost</t>
+          <t>Tăng Né Tránh</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Counterattack Boost</t>
+          <t>Tăng cường phản công</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Mid-air Attack Boost</t>
+          <t>Tăng Cường Mid-air Attack</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Echo Boost</t>
+          <t>Tăng Cường Echo</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Precision Strike</t>
+          <t>Đòn Tấn Công Chính Xác</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Focused Strike</t>
+          <t>Tập trung "Đòn Tấn Công"</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Terminal Velocity</t>
+          <t>Vận Tốc Giới Hạn</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Resonating Harmony</t>
+          <t>Hòa Âm Vang</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Grand Liberation</t>
+          <t>Đại Giải Phóng</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Triggered Healing</t>
+          <t>Đã kích hoạt Hồi Phục</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Echo Therapy</t>
+          <t>Trị Liệu Tiếng Vọng</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Shield Wall</t>
+          <t>Bức Tường Khiên</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Emergency Treatment</t>
+          <t>Điều Trị Khẩn Cấp</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Hoàn Thành Độ Khó I Cơn Nightmare Tái Hiện với 1400 Điểm</t>
+          <t>Hoàn thành Cơn Ác Mộng Tái Hiện Độ Khó I với 1400 điểm</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Hoàn Thành Độ Khó II Cơn Nightmare Tái Hiện với 1400 Điểm</t>
+          <t>Hoàn thành Cơn Ác Mộng Tái Hiện Độ Khó II với 1400 điểm</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Hoàn Thành Difficulty III Cơn Nightmare Tái Hiện với 2400 Điểm</t>
+          <t>Hoàn thành Cơn Ác Mộng Tái Hiện Độ Khó III với 2400 điểm</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Hoàn Thành Difficulty IV Cơn Nightmare Tái Hiện với 3200 Điểm</t>
+          <t>Hoàn thành Cơn Ác Mộng Tái Hiện Độ Khó IV với 3200 điểm</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Hoàn Thành Difficulty V Cơn Nightmare Tái Hiện với 3200 Điểm</t>
+          <t>Hoàn thành Cơn Ác Mộng Tái Hiện Độ Khó V với 3200 điểm</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Hoàn Thành Difficulty VI Cơn Nightmare Tái Hiện với 3800 Điểm</t>
+          <t>Hoàn thành Cơn Ác Mộng Tái Hiện Độ Khó VI với 3800 điểm</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Dreamscape Telephone Integrity Points</t>
+          <t>Điểm Toàn Vẹn Điện Thoại Mộng Ảo</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Time Points</t>
+          <t>Điểm Thời Gian</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Monster Points</t>
+          <t>Điểm quái vật</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Điểm thử thách</t>
+          <t>Điểm Thử Thách</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Time Consumed</t>
+          <t>Thời Gian Đã Tiêu Tốn</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Calamity Class</t>
+          <t>Hạng Thảm Họa</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Endless Arena</t>
+          <t>Đấu Trường Vô Tận</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Calamity Class</t>
+          <t>Hạng Thảm Họa</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Endless Arena</t>
+          <t>Đấu Trường Vô Tận</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Walk with the Dark</t>
+          <t>Đi trong Bóng Tối</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Light Phá Hủy Bùng Nổ</t>
+          <t>Kích Hoạt - Ánh Sáng Hủy Diệt</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>The Thật sự Lightning</t>
+          <t>Tia Chớp Chân Thật</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Saint Mode</t>
+          <t>Chế Độ Thánh</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Feline Infinite Booster</t>
+          <t>Tăng Cường Vô Hạn Feline</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>John Wicktorio: Không Nợ Nần Cho Kẻ Già</t>
+          <t>John Wicktorio: Không Nợ Cũ</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Phát Bắn Trong Khách Sạn: Buff Cơ Bản</t>
+          <t>Vết Súng tại Nhà Nghỉ: Tăng Cường Chính</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Phát Bắn Trong Khách Sạn: Buff Nâng Cao</t>
+          <t>Vụ Nổ Súng Tại Nhà Nghỉ: Hiệu ứng Nâng Cao</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Phát Bắn Trong Khách Sạn: Buff Tối Thượng</t>
+          <t>Vết Súng tại Nhà Nghỉ: Tăng Cường Tối Thượng</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Công Lý Phải Được Thực Thi: Buff Cơ Bản</t>
+          <t>Công Lý Sẽ Được Thực Thi: Tăng cường chính</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Công Lý Phải Được Thực Thi: Buff Nâng Cao</t>
+          <t>Công Lý Sẽ Được Thực Thi: Tăng cường nâng cao</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Công Lý Phải Được Thực Thi: Buff Tối Thượng</t>
+          <t>Công Lý Được Thực Thi: Tăng Cường Tối Thượng</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Crash and Burn: Primary Buff</t>
+          <t>Bùng Cháy: Hiệu Ứng Tăng Cường Cơ Bản</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Crash and Burn: Enhanced Buff</t>
+          <t>Bùng Cháy: Hiệu Ứng Tăng Cường Cấp Cao</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Crash and Burn: Ultimate Buff</t>
+          <t>Bùng Cháy: Hiệu Ứng Tăng Cường Tối Thượng</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Smash 'Em Tất cả: Primary Buff</t>
+          <t>Đập Phăng Tất Cả: Hiệu ứng Chính</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Smash 'Em Tất cả: Enhanced Buff</t>
+          <t>Đập Phăng Tất Cả: Hiệu ứng Nâng Cao</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Smash 'Em Tất cả: Ultimate Buff</t>
+          <t>Đập Phăng Tất Cả: Hiệu ứng Tối Thượng</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Right of Self-Defense: Primary Buff</t>
+          <t>Quyền Phòng Vệ Bản Thân: Hiệu ứng chính</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Right of Self-Defense: Enhanced Buff</t>
+          <t>Quyền Phòng Vệ Bản Thân: Hiệu ứng nâng cao</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Right of Self-Defense: Ultimate Buff</t>
+          <t>Quyền Phòng Vệ Chính Đáng: Tăng Cường Tối Thượng</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Play It Safe: Primary Buff</t>
+          <t>Thận Trọng: Hiệu ứng chính</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Play It Safe: Enhanced Buff</t>
+          <t>Thận Trọng: Hiệu ứng nâng cao</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Play It Safe: Ultimate Buff</t>
+          <t>Thận Trọng: Hiệu ứng tối thượng</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Phát Bắn Trong Khách Sạn: Buff Mặc Định</t>
+          <t>Vụ Nổ Súng Tại Nhà Nghỉ: Hiệu ứng Mặc Định</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Justice to be Served: Default Buff</t>
+          <t>Công Lý Sẽ Được Thực Thi: Tăng cường mặc định</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Crash and Burn: Default Buff</t>
+          <t>Bùng Cháy: Hiệu Ứng Tăng Cường Mặc Định</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Smash 'Em Tất cả: Default Buff</t>
+          <t>Đập Phăng Tất Cả: Hiệu ứng Mặc Định</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Right of Self-Defense: Default Buff</t>
+          <t>Quyền Phòng Vệ Bản Thân: Hiệu ứng mặc định</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Play It Safe: Default Buff</t>
+          <t>Thận Trọng: Hiệu ứng mặc định</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Thu thập 8.000 Xu trong "The Montellis"</t>
+          <t>Thu thập 8.000 Xu trong "Montellis"</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Thu thập 8.000 Xu trong "Fool's Fiction"</t>
+          <t>Thu thập 8.000 Xu trong "Hư Cấu Của Kẻ Ngốc"</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Thu thập 8.000 Xu trong "Once Upon a Time in Rinascita"</t>
+          <t>Thu thập 8.000 Xu trong "Ngày Xửa Ngày Xưa Ở Rinascita"</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Thu thập 8.000 Xu trong "City of Sentinel"</t>
+          <t>Thu thập 8.000 Xu trong "Thành Phố Cảnh Vệ"</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Thu thập 8.000 Xu trong "Echo Car Driver"</t>
+          <t>Thu thập 8.000 Xu trong "Tài Xế Xe Vọng Âm"</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Final Stage</t>
+          <t>Giai Đoạn Cuối</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Realm of Ego</t>
+          <t>Thế Giới Ảo Tưởng</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Major Forbidden Archive</t>
+          <t>Kho Lưu Trữ Tacet Cấm Chỉ</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Giáo Đoàn Vực Sâu</t>
+          <t>Lệnh của Vực Sâu</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Beyond Bức Màn Đỏ Thẫm</t>
+          <t>Vượt Qua Bức Màn Đỏ Thẫm</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Abyss of Initiation</t>
+          <t>Vực Khởi Đầu</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Abyss of Sacrifice</t>
+          <t>Vực Hy Sinh</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Abyss of Confession</t>
+          <t>Vực Thú Tội</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Garden Cứu Rỗi</t>
+          <t>Vườn Cứu Rỗi</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Garden Ngưỡng Mộ</t>
+          <t>Vườn Ngưỡng Mộ</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Bài Học Hư Không</t>
+          <t>Bài Học Vô Định</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Bài Học Than Hồng</t>
+          <t>Bài Học Tro Tàn</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Fallen Sanctum</t>
+          <t>Thánh Đường Sa Ngã</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Stricken Sanctum</t>
+          <t>Thánh Đường Tàn Tích</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Dance of White Ripple</t>
+          <t>Vũ Điệu Làn Sóng Trắng</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Striker Initiate-Linkage</t>
+          <t>Kết Nối Sơ Khởi - Đòn Đánh</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Dream Cosmos Suite</t>
+          <t>Bộ Điệu Vũ Cõi Mộng</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Dark Moon</t>
+          <t>Trăng Đen</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Devil Form</t>
+          <t>Hình Thái Ác Quỷ</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Oakheart Highcourt</t>
+          <t>Tòa Thượng Nghị Oakheart</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Knight of Atrocity</t>
+          <t>Hiệp Sĩ Tàn Ác</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Knight of Greed</t>
+          <t>Hiệp Sĩ Tham Lam</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Hiệp Sĩ của Sự Kiêu Ngạo</t>
+          <t>Hiệp Sĩ Hư Vinh</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Hiệp Sĩ của Sự Hèn Nhát</t>
+          <t>Hiệp Sĩ Hèn Nhát</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Hiệp Sĩ của Sự Vô Tri</t>
+          <t>Hiệp Sĩ Vô Tri</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Hiệp Sĩ của Trăng Huyết</t>
+          <t>Hiệp Sĩ Trăng Huyết</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Echo Challenge: Ảo Ảnh</t>
+          <t>Thử Thách Tiếng Vọng: Ảo Ảnh</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Đồi Hoàng Hôn</t>
+          <t>Thăng Bình Hoàng Hôn</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Đồi Tiếng Vang</t>
+          <t>Sự Trỗi Dậy Vang Dội</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Đồi Chỉ Huy</t>
+          <t>Lệnh Triệu Hồi</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Ruins Nơi Bóng Tối Lang Thang I</t>
+          <t>Tàn Tích Nơi Bóng Tối Lang Thang I</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Ruins Nơi Bóng Tối Lang Thang II</t>
+          <t>Tàn Tích Nơi Bóng Tối Lang Thang II</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Ruins Nơi Bóng Tối Lang Thang III</t>
+          <t>Tàn Tích Nơi Bóng Tối Lang Thang III</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Ruins Nơi Bóng Tối Lang Thang IV</t>
+          <t>Tàn Tích Nơi Bóng Tối Lang Thang IV</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Debris of Lumiscale Construct</t>
+          <t>Mảnh vỡ của Lumiscale Construct</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Fagaceae Formation</t>
+          <t>Hình Thành Fagaceae</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Storm Eye</t>
+          <t>Mắt Bão</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Ragunna City</t>
+          <t>Thành Phố Ragunna</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Penitent's End</t>
+          <t>Kết Cục Của Kẻ Ăn Năn</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Hallowed Reach</t>
+          <t>Thánh Vực</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Fagaceae Peninsula</t>
+          <t>Bán Đảo Fagaceae</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Beohr Waters</t>
+          <t>Vực Nước Beohr</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Avinoleum: Ground Remains</t>
+          <t>Avinoleum: Tàn Tích Mặt Đất</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Avinoleum: Sunken Remains</t>
+          <t>Avinoleum: Tàn Tích Chìm Đắm</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Titular Repository: Ruins</t>
+          <t>Kho Danh Hiệu: Tàn Tích</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Abyssal Crucible</t>
+          <t>Lò Luyện Vực Sâu</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Đại Sảnh Kiếm Thuật: Ruins</t>
+          <t>Đại Sảnh Kiếm Thuật: Tàn Tích</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Zargon Garden: Ruins</t>
+          <t>Vườn Zargon: Tàn Tích</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Tower Unity</t>
+          <t>Tháp Đoàn Kết</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Thánh Cột Hội Tụ</t>
+          <t>Tháp Thánh Hội Tụ</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Tower of Ascension</t>
+          <t>Tháp Thăng Hoa</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Tower of Salvation</t>
+          <t>Tháp Cứu Rỗi</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Beohr Trench</t>
+          <t>Hào Beohr</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Path of Bestowal</t>
+          <t>Con Đường Ban Tặng</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Titanbone Expanse</t>
+          <t>Vùng Đất Xương Titan</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Mournfell Canyon</t>
+          <t>Hẻm Núi Mournfell</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Border Mountains</t>
+          <t>Núi Biên Giới</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Minos Sewers</t>
+          <t>Cống ngầm Minos</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Capitoline Foothills</t>
+          <t>Chân đồi Capitoline</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Capitoline Hillside</t>
+          <t>Sườn Đồi Capitoline</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Capitoline Hilltop</t>
+          <t>Đỉnh Đồi Capitoline</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Thung Lũng Glory</t>
+          <t>Thung Lũng Vinh Quang</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Dragon of Dirge</t>
+          <t>Rồng Than Khóc</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Sentry Construct</t>
+          <t>Công Trình Tuần Tra</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Lioness of Glory</t>
+          <t>Sư Tử Vinh Quang - Giai Đoạn Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>The False Sovereign</t>
+          <t>Kẻ Quân Vương Giả Mạo</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Lady of the Sea</t>
+          <t>Nữ Thần Biển Cả</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Reactor Husk</t>
+          <t>Vỏ Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Hadrian's Gladiator</t>
+          <t>Đấu sĩ của Hadrian</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Aria Mummer</t>
+          <t>Diễn Viên Aria</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Farceur's Faces</t>
+          <t>Những Gương Mặt Hề Giả</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Signor Octopus</t>
+          <t>Ngài Bạch Tuộc</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Plushies Gang</t>
+          <t>Băng Đảng Thú Nhồi Bông</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Ảo Tưởng Không Trở Lại</t>
+          <t>Bản Hologram Chiến Thuật: Viễn Cảnh Không Lối Về</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Sentry Construct</t>
+          <t>Hologram Chiến Thuật: Cỗ Máy Canh Gác</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Hecate</t>
+          <t>Bản Hologram Chiến Thuật: Hecate</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Dragon of Dirge</t>
+          <t>Bản Hologram Chiến Thuật: Rồng Than Khóc</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Lorelei</t>
+          <t>Hologram Chiến Thuật: Lorelei</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Fleurdelys</t>
+          <t>Bản Hologram Chiến Thuật: Fleurdelys</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Kelpie</t>
+          <t>Hologram Chiến Thuật: Kelpie</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Lady of the Sea</t>
+          <t>Hologram Chiến Thuật: Nữ Chúa Biển Cả</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Lioness of Glory</t>
+          <t>Hologram Chiến Thuật: Sư Tử Nữ Hào Quang</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Tactic Hologram: The False Sovereign</t>
+          <t>Hologram Chiến Thuật: Kẻ Giả Mạo Quân Vương</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Dreamless</t>
+          <t>Bản Hologram Chiến Thuật: Dreamless</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Reactor Husk</t>
+          <t>Hologram Chiến Thuật: Xác Sống Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Hyvatia</t>
+          <t>Hologram Chiến Thuật: Hyvatia</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Sigillum</t>
+          <t>Hologram Chiến Thuật: Sigillum</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Vùng Đất Than Thở</t>
+          <t>Vùng Đất Than Khóc</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Bonus Challenge</t>
+          <t>Thử Thách Phần Thưởng</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Combat Rank A</t>
+          <t>Hạng Chiến Đấu A</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Combat Rank S</t>
+          <t>Hạng Chiến Đấu S</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Combat Rank SS</t>
+          <t>Hạng Chiến Đấu SS</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Đạt 1.000 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 1.000 điểm ở giai đoạn hiện tại.</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 2.000 điểm trong giai đoạn hiện tại</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Đạt 1.000 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 1.000 điểm ở giai đoạn hiện tại.</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 2.000 điểm trong giai đoạn hiện tại</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Đạt 1.000 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 1.000 điểm ở giai đoạn hiện tại.</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 2.000 điểm trong giai đoạn hiện tại</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Đạt 1.000 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 1.000 điểm ở giai đoạn hiện tại.</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 2.000 điểm trong giai đoạn hiện tại</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 2.000 điểm trong giai đoạn hiện tại</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Đạt 2.000 điểm ở giai đoạn hiện tại</t>
+          <t>Đạt 2.000 điểm trong giai đoạn hiện tại</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Apex Ragunna</t>
+          <t>Ragunna Đỉnh Cao</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Mysterious Sea Chest</t>
+          <t>Rương Biển Bí Ẩn</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Raging Command I</t>
+          <t>Mệnh Lệnh Cuồng Nộ I</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Raging Command II</t>
+          <t>Mệnh Lệnh Cuồng Nộ II</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Raging Command III</t>
+          <t>Mệnh Lệnh Cuồng Nộ III</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Raging Command IV</t>
+          <t>Mệnh Lệnh Cuồng Nộ IV</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Raging Command V</t>
+          <t>Mệnh Lệnh Cuồng Nộ V</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Raging Command VI</t>
+          <t>Mệnh Lệnh Cuồng Nộ VI</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Raging Command VII</t>
+          <t>Mệnh Lệnh Cuồng Nộ VII</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Shattered Glaciers I</t>
+          <t>Băng Hà Vỡ Tan I</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Shattered Glaciers II</t>
+          <t>Băng Hà Vỡ Tan II</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Shattered Glaciers III</t>
+          <t>Băng Vỡ III</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Eternal Aegis I</t>
+          <t>Lớp Khiên Vĩnh Hằng I</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Eternal Aegis II</t>
+          <t>Lớp Khiên Vĩnh Hằng II</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Eternal Aegis III</t>
+          <t>Lớp Khiên Vĩnh Hằng III</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Resonant Crescendo I</t>
+          <t>Cộng Hưởng Cao Trào I</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Resonant Crescendo II</t>
+          <t>Cộng Hưởng Cao Trào II</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Resonant Crescendo III</t>
+          <t>Cộng Hưởng Cao Trào III</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Raging Strikes</t>
+          <t>Đòn Đánh Cuồng Nộ</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Vital Core</t>
+          <t>Lõi Sinh Tồn</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Shield's Embrace</t>
+          <t>Bảo Vệ Vững Chắc</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Glacio Antibody</t>
+          <t>Kháng Thể Glacio</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Fusion Antibody</t>
+          <t>Kháng Thể Hợp Nhất</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Electro Antibody</t>
+          <t>Kháng Thể Electro</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Aero Antibody</t>
+          <t>Kháng thể Aero</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Spectro Antibody</t>
+          <t>Kháng thể Spectro</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Havoc Antibody</t>
+          <t>Kháng Thể Havoc</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Fury Strike</t>
+          <t>Đòn Phẫn Nộ</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Armor Shatter</t>
+          <t>Phá Giáp</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Burst Strike</t>
+          <t>Đòn Bùng Nổ</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Piercing Strike</t>
+          <t>Đòn Tấn Công Xuyên Thấu</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Ultimate Strike</t>
+          <t>Đòn Tối Thượng</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Razor Fury</t>
+          <t>Cơn Thịnh Nộ Của Razor</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Rampage Liberation</t>
+          <t>Giải Phóng Cuồng Nộ</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Resonant Symphony</t>
+          <t>Bản Giao Hưởng Cộng Hưởng</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Glacial Bite</t>
+          <t>Cắn Băng Giá</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Infernal Blaze</t>
+          <t>Hỏa Diệm Địa Ngục</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Thunderclap</t>
+          <t>Tiếng Sấm</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Howling Gale</t>
+          <t>Cuồng Phong Gào Thét</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Etheral Halo</t>
+          <t>Vầng Hào Quang Không Gian</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Awakening Umbra</t>
+          <t>Bóng Tối Thức Tỉnh</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Lạc giữa biển khơi</t>
+          <t>Lạc Trên Biển Cả</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>The Triangle</t>
+          <t>Tam Giác Định Mệnh</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Trapped in Loop</t>
+          <t>Bị kẹt trong vòng lặp</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Deadly Wish</t>
+          <t>Ước Nguyện Tử Thần</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Paranoid Hope</t>
+          <t>Niềm Hy Vọng Điên Cuồng</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Realm of Rebirth</t>
+          <t>Tổ Tacet Tái Sinh</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Cursed Town</t>
+          <t>Thị trấn bị nguyền rủa</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Into the Deadlight</t>
+          <t>Vào Ánh Sáng Chết</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Time Relived</t>
+          <t>Thời Gian Tái Sinh</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Nowhere to Hide</t>
+          <t>Không chỗ ẩn náu</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Endless Dream</t>
+          <t>Giấc Mơ Vô Tận</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Nightmare Attack</t>
+          <t>Tấn Công Ác Mộng</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Paranormal Event</t>
+          <t>Sự Kiện Siêu Nhiên</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Brief Respite</t>
+          <t>Khoảnh Khắc Nghỉ Ngơi</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Exorcism Ritual</t>
+          <t>Nghi Thức Trừ Tà</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Abyssal Gaze</t>
+          <t>Ánh Mắt Vực Sâu</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Visitor from Beyond</t>
+          <t>Vị Khách Từ Phương Xa</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Tangled Fate</t>
+          <t>Số Phận Rối Bời</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Dragon of Dirge</t>
+          <t>Rồng Than Khóc</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Chest Mimic</t>
+          <t>Rương Biến Hình</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Đạt 1.000 Tactic Points ở Penitent's End I</t>
+          <t>Đạt 1.000 Điểm Chiến Thuật trong Penitent's End I</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Đạt 1.000 Tactic Points ở Penitent's End II</t>
+          <t>Đạt 1.000 Điểm Chiến Thuật trong Penitent's End II</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Đạt 1.000 Tactic Points ở Penitent's End III</t>
+          <t>Đạt 1.000 Điểm Chiến Thuật trong Penitent's End III</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Đạt 1.000 Tactic Points ở Penitent's End IV</t>
+          <t>Đạt 1.000 Điểm Chiến Thuật trong Penitent's End IV</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Đạt 1.000 Tactic Points ở Penitent's End V</t>
+          <t>Đạt 1.000 Điểm Chiến Thuật trong Penitent's End V</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Restoration Station</t>
+          <t>Trạm Phục Hồi</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Flight Point</t>
+          <t>Điểm Bay</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Data's Gift I</t>
+          <t>Món Quà Từ Dữ Liệu I</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Data's Gift II</t>
+          <t>Món Quà Từ Dữ Liệu II</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Legendary Fish King</t>
+          <t>Vua Cá Huyền Thoại</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>The Wheel of Broken Fate</t>
+          <t>Vòng Xoay Định Mệnh Tan Vỡ</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Whispers Between Stars - Lynae</t>
+          <t>Lời Thì Thầm Giữa Các Vì Sao - Lynae</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Hoàn thành chiến đấu tại vị trí chỉ định</t>
+          <t>Hoàn thành trận chiến tại địa điểm chỉ định</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Chụp ảnh tại vị trí chỉ định</t>
+          <t>Chụp ảnh tại vị trí đã định</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Whispers Between Stars - Mornye</t>
+          <t>Lời Thì Thầm Giữa Các Vì Sao - Mornye</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Hoàn thành chiến đấu tại vị trí chỉ định</t>
+          <t>Hoàn thành trận chiến tại địa điểm chỉ định</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Chụp ảnh tại vị trí chỉ định</t>
+          <t>Chụp ảnh tại vị trí đã định</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Whispers Between Stars - Luuk Herssen</t>
+          <t>Lời Thì Thầm Giữa Các Vì Sao - Luuk Herssen</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Hoàn thành chiến đấu tại vị trí chỉ định</t>
+          <t>Hoàn thành trận chiến tại địa điểm chỉ định</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Chụp ảnh tại vị trí chỉ định</t>
+          <t>Chụp ảnh tại vị trí đã định</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Whispers Between Stars - Lucilla</t>
+          <t>Lời Thì Thầm Giữa Các Vì Sao - Lucilla</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Hoàn thành chiến đấu tại vị trí chỉ định</t>
+          <t>Hoàn thành trận chiến tại địa điểm chỉ định</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Chụp ảnh tại vị trí chỉ định</t>
+          <t>Chụp ảnh tại vị trí đã định</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Threat Elimination</t>
+          <t>Loại Bỏ Mối Đe Dọa</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Ragunna Weather Forecast</t>
+          <t>Dự Báo Thời Tiết Ragunna</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Cubie Derby</t>
+          <t>Đua Cubie</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Jinhsi Cube</t>
+          <t>Khối Kim Tư</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Changli Cube</t>
+          <t>Khối Changli</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Calcharo Cube</t>
+          <t>Khối Calcharo</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Shorekeeper Cube</t>
+          <t>Khối Shorekeeper</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Camellya Cube</t>
+          <t>Khối Camellya</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Carlotta Cube</t>
+          <t>Khối Carlotta</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Roccia Cube</t>
+          <t>Khối lập phương Roccia</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Brant Cube</t>
+          <t>Khối Brant</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Cantarella Cube</t>
+          <t>Khối Cantarella</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Zani Cube</t>
+          <t>Khối Zani</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Cartethyia Cube</t>
+          <t>Khối Cartethyia</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Phoebe Cube</t>
+          <t>Khối Phoebe</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Rover Cube</t>
+          <t>Khối Lập Phương của Vận Mệnh Giả</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Rover Cube</t>
+          <t>Khối Lập Phương của Vận Mệnh Giả</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>The Final Has Ended</t>
+          <t>Đã Hết... Kết Cục Cuối Cùng</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>The Match Has Ended</t>
+          <t>Trận Đấu Đã Kết Thúc</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Giai đoạn Hỗ trợ kết thúc sau</t>
+          <t>Giai Đoạn Hỗ Trợ Kết Thúc Trong</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Next Hỗ Trợ Giai đoạn In</t>
+          <t>Giai Đoạn Hỗ Trợ Tiếp Theo Trong</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>The Final Has Ended</t>
+          <t>Đã Hết... Kết Cục Cuối Cùng</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Không Có Cube Được Hỗ Trợ</t>
+          <t>Không có Khối Lập phương Hỗ trợ</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Bảng A Vòng bảng - Hiệp 1</t>
+          <t>Bảng A CK - Hiệp 1</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Bảng A Vòng bảng - Hiệp 2</t>
+          <t>Bảng A CK - Hiệp 2</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Bảng A Tứ kết - Hiệp 1</t>
+          <t>Bảng A TK - Hiệp 1</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Bảng A Tứ kết - Hiệp 2</t>
+          <t>Bảng A TK - Hiệp 2</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Bảng B Vòng bảng - Hiệp 1</t>
+          <t>Bảng B GS - Hiệp 1</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Bảng B Vòng bảng - Hiệp 2</t>
+          <t>Bảng B GS - Hiệp 2</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Bảng B Tứ kết - Hiệp 1</t>
+          <t>Bảng B TK - Hiệp 1</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Bảng B Tứ kết - Hiệp 2</t>
+          <t>Bảng B TK - Hiệp 2</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Final - 1st Half</t>
+          <t>Đoạn Kết - Nửa Đầu</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Final - 2nd Half</t>
+          <t>Đoạn Kết - Nửa Sau</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Race</t>
+          <t>Đua</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Rewards</t>
+          <t>Phần thưởng</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Popularity</t>
+          <t>Độ nổi tiếng</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Patrons</t>
+          <t>Những Người Bảo Trợ</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>2nd Half Starting Positions</t>
+          <t>Vị Trí Xuất Phát Hiệp 2</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Watch Replay</t>
+          <t>Xem Lại</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Match Complete</t>
+          <t>Trận đấu kết thúc</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Bảng A Vòng bảng - Hiệp 1</t>
+          <t>Bảng A CK - Hiệp 1</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Bảng A Vòng bảng - Hiệp 2</t>
+          <t>Bảng A CK - Hiệp 2</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Tứ kết Bảng A - Hiệp 1</t>
+          <t>Bảng A TK - Hiệp 1</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Tứ kết Bảng A - Hiệp 2</t>
+          <t>Bảng A TK - Hiệp 2</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Vòng bảng Bảng B - Hiệp 1</t>
+          <t>Bảng B GS - Hiệp 1</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Vòng bảng Bảng B - Hiệp 2</t>
+          <t>Bảng B GS - Hiệp 2</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Tứ kết Bảng B - Hiệp 1</t>
+          <t>Bảng B TK - Hiệp 1</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Tứ kết Bảng B - Hiệp 2</t>
+          <t>Bảng B TK - Hiệp 2</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Final - 1st Half</t>
+          <t>Đoạn Kết - Nửa Đầu</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Final - 2nd Half</t>
+          <t>Đoạn Kết - Nửa Sau</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Cube Advanced</t>
+          <t>Khối Lập Phương Cao Cấp</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Total Popularity</t>
+          <t>Tổng Độ Phổ Biến</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Underdog Odds</t>
+          <t>Cơ hội của kẻ yếu thế</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Popularity Return</t>
+          <t>Hoàn trả độ nổi tiếng</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Không Có Cube Được Hỗ Trợ</t>
+          <t>Không có Khối Lập phương Hỗ trợ</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Advances</t>
+          <t>Tiến công</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Champion</t>
+          <t>Quán Quân</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>The Cubes are warming up</t>
+          <t>Các Khối lập phương đang khởi động</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Group A - Group Stage</t>
+          <t>Bảng A - Vòng Bảng</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Group A - Quarterfinal</t>
+          <t>Bảng A - Tứ kết</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Group B - Group Stage</t>
+          <t>Bảng B - Vòng Bảng</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Group B - Quarterfinal</t>
+          <t>Bảng B - Vòng Tứ Kết</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Đoạn Kết</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Hỗ Trợ Cube</t>
+          <t>Khối Hỗ Trợ</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Được Hỗ Trợ</t>
+          <t>Đã ủng hộ</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Popularity Ratio</t>
+          <t>Tỷ lệ nổi tiếng</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Total Popularity</t>
+          <t>Tổng Độ Phổ Biến</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Popularity Return</t>
+          <t>Hoàn trả độ nổi tiếng</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Next Underdog Odds Đặt lại Time</t>
+          <t>Thời Gian Đặt Lại Tỷ Lệ Thua Tiếp Theo</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Hỗ Trợ Giai đoạn Ends In</t>
+          <t>Giai Đoạn Hỗ Trợ Kết Thúc Trong</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Đang Hỗ Trợ</t>
+          <t>Đang ủng hộ</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Đã hủy</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Underdog Odds</t>
+          <t>Cơ hội của kẻ yếu thế</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Hỗ Trợ Underdog Odds</t>
+          <t>Tỷ Lệ Thua Lợi</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Popularity Changes</t>
+          <t>Biến động độ nổi tiếng</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Được Hỗ Trợ</t>
+          <t>Đã ủng hộ</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,8 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Xác nhận
-NAME_TITLE_002242432:::Vòng đua</t>
+          <t>Xác nhận</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35435,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Underdog</t>
+          <t>Kẻ yếu thế</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35505,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Race Stage</t>
+          <t>Sân đua</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
